--- a/jogos_2024-11-27.xlsx
+++ b/jogos_2024-11-27.xlsx
@@ -643,25 +643,25 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Samtredia</t>
+          <t>Dinamo Tbilisi</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dila</t>
+          <t>Dinamo Batumi</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
@@ -669,83 +669,83 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>4.8</v>
+        <v>1.98</v>
       </c>
       <c r="M2" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N2" t="n">
-        <v>1.55</v>
+        <v>3.2</v>
       </c>
       <c r="O2" t="n">
-        <v>4.75</v>
+        <v>2.5</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.25</v>
+        <v>4.33</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S2" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="T2" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="U2" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="V2" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W2" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="X2" t="n">
-        <v>3.55</v>
+        <v>3.26</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.95</v>
+        <v>3.35</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>['9004']</t>
+          <t>['15', '27']</t>
         </is>
       </c>
       <c r="AG2" t="n">
-        <v>1.88</v>
+        <v>1.22</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.17</v>
+        <v>1.66</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.25</v>
+        <v>1.67</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="AK2" s="3" t="n">
         <v>45623.29166666666</v>
@@ -772,25 +772,25 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Dinamo Tbilisi</t>
+          <t>Samtredia</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dinamo Batumi</t>
+          <t>Dila</t>
         </is>
       </c>
       <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="n">
         <v>1</v>
       </c>
-      <c r="H3" t="n">
-        <v>2</v>
-      </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K3" t="inlineStr">
         <is>
@@ -798,83 +798,83 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>1.98</v>
+        <v>4.8</v>
       </c>
       <c r="M3" t="n">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="N3" t="n">
-        <v>3.2</v>
+        <v>1.55</v>
       </c>
       <c r="O3" t="n">
-        <v>2.5</v>
+        <v>4.75</v>
       </c>
       <c r="P3" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.33</v>
+        <v>2.25</v>
       </c>
       <c r="R3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S3" t="n">
+        <v>3</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="U3" t="n">
         <v>1.43</v>
       </c>
-      <c r="S3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T3" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U3" t="n">
+      <c r="V3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X3" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>['9004']</t>
+        </is>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AJ3" t="n">
         <v>1.4</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="X3" t="n">
-        <v>3.26</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>['58']</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>['15', '27']</t>
-        </is>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>2.5</v>
       </c>
       <c r="AK3" s="3" t="n">
         <v>45623.29166666666</v>
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Vardar</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>KF Gostivari</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -919,7 +919,7 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
@@ -927,62 +927,62 @@
         </is>
       </c>
       <c r="L4" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M4" t="n">
         <v>3</v>
       </c>
-      <c r="M4" t="n">
-        <v>3.3</v>
-      </c>
       <c r="N4" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S4" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T4" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X4" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AC4" t="n">
         <v>2.1</v>
       </c>
-      <c r="O4" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="P4" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="U4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X4" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Z4" t="n">
+      <c r="AD4" t="n">
         <v>1.65</v>
       </c>
-      <c r="AA4" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AE4" t="inlineStr">
         <is>
           <t>[]</t>
@@ -990,20 +990,20 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>['63', '87']</t>
+          <t>['6', '37']</t>
         </is>
       </c>
       <c r="AG4" t="n">
-        <v>1.57</v>
+        <v>1.44</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AI4" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ4" t="n">
         <v>2.4</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.73</v>
       </c>
       <c r="AK4" s="3" t="n">
         <v>45623.375</v>
@@ -1030,23 +1030,23 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Besa Dobërdoll</t>
+          <t>Struga</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Akademija Pandev</t>
+          <t>Pelister</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="M5" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" t="n">
+        <v>7</v>
+      </c>
+      <c r="O5" t="n">
         <v>2</v>
       </c>
-      <c r="M5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N5" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T5" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="X5" t="n">
         <v>2.6</v>
       </c>
-      <c r="P5" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R5" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T5" t="n">
+      <c r="Y5" t="n">
         <v>2.55</v>
       </c>
-      <c r="U5" t="n">
+      <c r="Z5" t="n">
         <v>1.45</v>
       </c>
-      <c r="V5" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W5" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X5" t="n">
-        <v>4</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2</v>
-      </c>
       <c r="AA5" t="n">
-        <v>2.75</v>
+        <v>4.8</v>
       </c>
       <c r="AB5" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>['18']</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG5" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AI5" t="n">
         <v>1.4</v>
       </c>
-      <c r="AC5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>['61']</t>
-        </is>
-      </c>
-      <c r="AG5" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AJ5" t="n">
-        <v>2.5</v>
+        <v>4.2</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45623.375</v>
@@ -1159,19 +1159,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Struga</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Pelister</t>
+          <t>Voska Sport</t>
         </is>
       </c>
       <c r="G6" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" t="n">
         <v>1</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -1185,80 +1185,80 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="M6" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="N6" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>2.4</v>
+        <v>2.85</v>
       </c>
       <c r="T6" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="U6" t="n">
-        <v>1.28</v>
+        <v>1.41</v>
       </c>
       <c r="V6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X6" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>['23', '65', '76', '78']</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>['74']</t>
+        </is>
+      </c>
+      <c r="AG6" t="n">
         <v>1.06</v>
       </c>
-      <c r="W6" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="X6" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="Y6" t="n">
+      <c r="AH6" t="n">
         <v>2.55</v>
       </c>
-      <c r="Z6" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>['18']</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="AH6" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AI6" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AJ6" t="n">
         <v>4.2</v>
@@ -1288,109 +1288,109 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Tikveš</t>
+          <t>Besa Dobërdoll</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
+      <c r="M7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X7" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z7" t="n">
         <v>2</v>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="M7" t="n">
-        <v>3</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S7" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X7" t="n">
-        <v>3</v>
-      </c>
-      <c r="Y7" t="n">
+      <c r="AA7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>2.5</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>['6', '37']</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>2.4</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45623.375</v>
@@ -1546,22 +1546,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Sileks</t>
+          <t>Vardar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Voska Sport</t>
+          <t>KF Gostivari</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1572,37 +1572,37 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>1.26</v>
+        <v>3</v>
       </c>
       <c r="M9" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
-        <v>10</v>
+        <v>2.1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.83</v>
+        <v>3.75</v>
       </c>
       <c r="P9" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>8</v>
+        <v>2.88</v>
       </c>
       <c r="R9" t="n">
         <v>1.36</v>
       </c>
       <c r="S9" t="n">
-        <v>2.85</v>
+        <v>2.88</v>
       </c>
       <c r="T9" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="U9" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="V9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="W9" t="n">
         <v>1.25</v>
@@ -1611,10 +1611,10 @@
         <v>3.6</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AA9" t="n">
         <v>3.3</v>
@@ -1623,32 +1623,32 @@
         <v>1.29</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AD9" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>['63', '87']</t>
+        </is>
+      </c>
+      <c r="AG9" t="n">
         <v>1.57</v>
       </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>['23', '65', '76', '78']</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>['74']</t>
-        </is>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AH9" t="n">
-        <v>2.55</v>
+        <v>1.27</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="AJ9" t="n">
-        <v>4.2</v>
+        <v>1.73</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45623.375</v>
@@ -2062,22 +2062,22 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Remo Stars</t>
+          <t>Enugu Rangers</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shooting Stars</t>
+          <t>Lobi Stars</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
@@ -2088,65 +2088,65 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>['45+3', '67']</t>
+          <t>['26', '30', '44']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45623.5</v>
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sunshine Stars</t>
+          <t>Akwa United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rivers United</t>
+          <t>Plateau United</t>
         </is>
       </c>
       <c r="G14" t="n">
         <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.86</v>
+        <v>1.45</v>
       </c>
       <c r="M14" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="N14" t="n">
+        <v>7</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X14" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['90+9']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AJ14" t="n">
         <v>4.75</v>
-      </c>
-      <c r="O14" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="P14" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="T14" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="X14" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>['61']</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['3']</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AJ14" t="n">
-        <v>3.34</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45623.5</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Montenegro Montenegrin First League</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Petrovac</t>
+          <t>Bayelsa United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Budućnost</t>
+          <t>Niger Tornadoes</t>
         </is>
       </c>
       <c r="G15" t="n">
+        <v>4</v>
+      </c>
+      <c r="H15" t="n">
         <v>1</v>
       </c>
-      <c r="H15" t="n">
-        <v>4</v>
-      </c>
       <c r="I15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.8</v>
+        <v>1.7</v>
       </c>
       <c r="M15" t="n">
         <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>1.8</v>
+        <v>4.5</v>
       </c>
       <c r="O15" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="P15" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>6.5</v>
       </c>
       <c r="R15" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>['16', '23', '48', '62']</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>['81']</t>
+        </is>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AI15" t="n">
         <v>1.44</v>
       </c>
-      <c r="S15" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X15" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>2</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>['15']</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>['1', '55', '68', '90+5']</t>
-        </is>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AJ15" t="n">
-        <v>1.8</v>
+        <v>4</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45623.5</v>
@@ -2439,35 +2439,35 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2024/2025</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Telavi</t>
+          <t>Sunshine Stars</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Samgurali</t>
+          <t>Rivers United</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.58</v>
+        <v>1.86</v>
       </c>
       <c r="M16" t="n">
-        <v>3.06</v>
+        <v>2.8</v>
       </c>
       <c r="N16" t="n">
-        <v>2.71</v>
+        <v>4.75</v>
       </c>
       <c r="O16" t="n">
-        <v>3.1</v>
+        <v>2.65</v>
       </c>
       <c r="P16" t="n">
-        <v>2.1</v>
+        <v>1.8</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.2</v>
+        <v>5.25</v>
       </c>
       <c r="R16" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="S16" t="n">
-        <v>2.6</v>
+        <v>1.95</v>
       </c>
       <c r="T16" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>3.19</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC16" t="n">
         <v>2.75</v>
       </c>
-      <c r="U16" t="n">
+      <c r="AD16" t="n">
         <v>1.4</v>
       </c>
-      <c r="V16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X16" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.35</v>
+        <v>1.16</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AI16" t="n">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="AJ16" t="n">
-        <v>2.1</v>
+        <v>3.34</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45623.5</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oman Professional League</t>
+          <t>Nigeria NPFL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2578,16 +2578,16 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ibri</t>
+          <t>Remo Stars</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Al Khabourah</t>
+          <t>Shooting Stars</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="M17" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N17" t="n">
+        <v>7</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>12</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="T17" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Y17" t="n">
         <v>3.1</v>
       </c>
-      <c r="N17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O17" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P17" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="X17" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="Y17" t="n">
+      <c r="Z17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['45+3', '67']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AH17" t="n">
         <v>2.5</v>
       </c>
-      <c r="Z17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>['10']</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
+      <c r="AI17" t="n">
         <v>1.3</v>
       </c>
-      <c r="AH17" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AJ17" t="n">
-        <v>2.4</v>
+        <v>7</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45623.5</v>
@@ -2707,22 +2707,22 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Enugu Rangers</t>
+          <t>Ikorodu City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lobi Stars</t>
+          <t>El Kanemi Warriors</t>
         </is>
       </c>
       <c r="G18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>['26', '30', '44']</t>
+          <t>['62', '77']</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -2955,32 +2955,32 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2024/2025</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Kwara United</t>
+          <t>Telavi</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Heartland</t>
+          <t>Samgurali</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -2991,65 +2991,65 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.48</v>
+        <v>2.58</v>
       </c>
       <c r="M20" t="n">
-        <v>3.7</v>
+        <v>3.06</v>
       </c>
       <c r="N20" t="n">
-        <v>6</v>
+        <v>2.71</v>
       </c>
       <c r="O20" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P20" t="n">
         <v>2.1</v>
       </c>
-      <c r="P20" t="n">
+      <c r="Q20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X20" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="Y20" t="n">
         <v>1.95</v>
       </c>
-      <c r="Q20" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="T20" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X20" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>2.5</v>
-      </c>
       <c r="Z20" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="AA20" t="n">
-        <v>4.75</v>
+        <v>3.35</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.1</v>
+        <v>1.28</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.75</v>
+        <v>1.77</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.4</v>
+        <v>1.94</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['21']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -3058,16 +3058,16 @@
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.15</v>
+        <v>1.41</v>
       </c>
       <c r="AI20" t="n">
-        <v>1.36</v>
+        <v>1.91</v>
       </c>
       <c r="AJ20" t="n">
-        <v>4.75</v>
+        <v>2.1</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45623.5</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Oman Professional League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,23 +3094,23 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Bayelsa United</t>
+          <t>Ibri</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Niger Tornadoes</t>
+          <t>Al Khabourah</t>
         </is>
       </c>
       <c r="G21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>1</v>
       </c>
-      <c r="I21" t="n">
-        <v>2</v>
-      </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="N21" t="n">
-        <v>4.5</v>
+        <v>2.8</v>
       </c>
       <c r="O21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="X21" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>['10']</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AJ21" t="n">
         <v>2.4</v>
-      </c>
-      <c r="P21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="T21" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="V21" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="X21" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>5.65</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['16', '23', '48', '62']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>['81']</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>4</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45623.5</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Nigeria NPFL</t>
+          <t>Montenegro Montenegrin First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,109 +3223,109 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ikorodu City</t>
+          <t>Petrovac</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>El Kanemi Warriors</t>
+          <t>Budućnost</t>
         </is>
       </c>
       <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>4</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L22" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="N22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X22" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="Y22" t="n">
         <v>2</v>
       </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['62', '77']</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['1', '55', '68', '90+5']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45623.5</v>
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Akwa United</t>
+          <t>Kwara United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plateau United</t>
+          <t>Heartland</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3367,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="M23" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O23" t="n">
         <v>2.1</v>
@@ -3396,47 +3396,47 @@
         <v>7.5</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.48</v>
       </c>
       <c r="S23" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="T23" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="U23" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="V23" t="n">
-        <v>1.02</v>
+        <v>1.09</v>
       </c>
       <c r="W23" t="n">
-        <v>1.38</v>
+        <v>1.5</v>
       </c>
       <c r="X23" t="n">
-        <v>2.85</v>
+        <v>2.4</v>
       </c>
       <c r="Y23" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>3.85</v>
+        <v>4.75</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.42</v>
+        <v>2.75</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['90+9']</t>
+          <t>['21']</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3445,13 +3445,13 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AJ23" t="n">
         <v>4.75</v>
@@ -3610,19 +3610,19 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Saburtalo</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Kolkheti Poti</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I25" t="n">
         <v>1</v>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.4</v>
+        <v>1.32</v>
       </c>
       <c r="M25" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="N25" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="O25" t="n">
-        <v>2</v>
+        <v>1.62</v>
       </c>
       <c r="P25" t="n">
-        <v>2.38</v>
+        <v>2.88</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.5</v>
+        <v>7</v>
       </c>
       <c r="R25" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="S25" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="T25" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
       <c r="U25" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="V25" t="n">
         <v>1.01</v>
       </c>
       <c r="W25" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X25" t="n">
-        <v>4.8</v>
+        <v>7</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.65</v>
+        <v>1.51</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.55</v>
+        <v>2.2</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AD25" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['45+7', '76']</t>
+          <t>['8']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['73']</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AJ25" t="n">
-        <v>3.5</v>
+        <v>4.33</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45623.54166666666</v>
@@ -3739,19 +3739,19 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Saburtalo</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kolkheti Poti</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.32</v>
+        <v>1.4</v>
       </c>
       <c r="M26" t="n">
-        <v>4.6</v>
+        <v>4.1</v>
       </c>
       <c r="N26" t="n">
-        <v>7.5</v>
+        <v>6.25</v>
       </c>
       <c r="O26" t="n">
-        <v>1.62</v>
+        <v>2</v>
       </c>
       <c r="P26" t="n">
-        <v>2.88</v>
+        <v>2.38</v>
       </c>
       <c r="Q26" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="T26" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="U26" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="V26" t="n">
         <v>1.01</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="X26" t="n">
-        <v>7</v>
+        <v>4.8</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.51</v>
+        <v>1.65</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.32</v>
+        <v>2.1</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.58</v>
+        <v>1.45</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['8']</t>
+          <t>['45+7', '76']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['73']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="AH26" t="n">
-        <v>2.75</v>
+        <v>2.25</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.2</v>
+        <v>1.33</v>
       </c>
       <c r="AJ26" t="n">
-        <v>4.33</v>
+        <v>3.5</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45623.54166666666</v>
@@ -3997,22 +3997,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Cape Town City</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Richards Bay</t>
+          <t>Polokwane City</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -4023,43 +4023,43 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.67</v>
+        <v>1.98</v>
       </c>
       <c r="M28" t="n">
-        <v>3.32</v>
+        <v>3.08</v>
       </c>
       <c r="N28" t="n">
-        <v>5.25</v>
+        <v>3.84</v>
       </c>
       <c r="O28" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="P28" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="S28" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="T28" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="U28" t="n">
         <v>1.25</v>
       </c>
       <c r="V28" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W28" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="X28" t="n">
-        <v>2.4</v>
+        <v>2.37</v>
       </c>
       <c r="Y28" t="n">
         <v>2.55</v>
@@ -4071,35 +4071,35 @@
         <v>5</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AE28" t="inlineStr">
         <is>
-          <t>['21', '68']</t>
+          <t>['56']</t>
         </is>
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>['90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG28" t="n">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.86</v>
+        <v>1.6</v>
       </c>
       <c r="AI28" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AJ28" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45623.60416666666</v>
@@ -4126,22 +4126,22 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Cape Town City</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Polokwane City</t>
+          <t>Richards Bay</t>
         </is>
       </c>
       <c r="G29" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" t="n">
         <v>1</v>
       </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -4152,43 +4152,43 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.98</v>
+        <v>1.67</v>
       </c>
       <c r="M29" t="n">
-        <v>3.08</v>
+        <v>3.32</v>
       </c>
       <c r="N29" t="n">
-        <v>3.84</v>
+        <v>5.25</v>
       </c>
       <c r="O29" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="P29" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q29" t="n">
-        <v>4.5</v>
+        <v>5.5</v>
       </c>
       <c r="R29" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="S29" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="T29" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="U29" t="n">
         <v>1.25</v>
       </c>
       <c r="V29" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W29" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="X29" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="Y29" t="n">
         <v>2.55</v>
@@ -4200,35 +4200,35 @@
         <v>5</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AD29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>['21', '68']</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>['90+1']</t>
+        </is>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AI29" t="n">
         <v>1.57</v>
       </c>
-      <c r="AE29" t="inlineStr">
-        <is>
-          <t>['56']</t>
-        </is>
-      </c>
-      <c r="AF29" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ29" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="AK29" s="3" t="n">
         <v>45623.60416666666</v>
@@ -4513,25 +4513,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>CD Castellón</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G32" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K32" t="inlineStr">
         <is>
@@ -4539,80 +4539,80 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.79</v>
+        <v>1.63</v>
       </c>
       <c r="M32" t="n">
-        <v>3.7</v>
+        <v>4.15</v>
       </c>
       <c r="N32" t="n">
-        <v>4.45</v>
+        <v>5</v>
       </c>
       <c r="O32" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="P32" t="n">
-        <v>2.05</v>
+        <v>2.25</v>
       </c>
       <c r="Q32" t="n">
-        <v>5</v>
+        <v>4.75</v>
       </c>
       <c r="R32" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S32" t="n">
-        <v>2.62</v>
+        <v>2.9</v>
       </c>
       <c r="T32" t="n">
-        <v>2.95</v>
+        <v>2.7</v>
       </c>
       <c r="U32" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="V32" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W32" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="X32" t="n">
-        <v>3.17</v>
+        <v>3.65</v>
       </c>
       <c r="Y32" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.81</v>
+        <v>1.99</v>
       </c>
       <c r="AA32" t="n">
-        <v>3.71</v>
+        <v>3.2</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['14', '33', '81', '90+5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>['16', '41']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG32" t="n">
         <v>1.15</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="AI32" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AJ32" t="n">
         <v>2.95</v>
@@ -4642,25 +4642,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CD Castellón</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4668,80 +4668,80 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.63</v>
+        <v>1.79</v>
       </c>
       <c r="M33" t="n">
-        <v>4.15</v>
+        <v>3.7</v>
       </c>
       <c r="N33" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q33" t="n">
         <v>5</v>
       </c>
-      <c r="O33" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>4.75</v>
-      </c>
       <c r="R33" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S33" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W33" t="n">
         <v>1.36</v>
       </c>
-      <c r="S33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V33" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W33" t="n">
+      <c r="X33" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="AB33" t="n">
         <v>1.28</v>
       </c>
-      <c r="X33" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AC33" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.83</v>
+        <v>1.73</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['14', '33', '81', '90+5']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['16', '41']</t>
         </is>
       </c>
       <c r="AG33" t="n">
         <v>1.15</v>
       </c>
       <c r="AH33" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AJ33" t="n">
         <v>2.95</v>
@@ -5287,25 +5287,25 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G38" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K38" t="inlineStr">
         <is>
@@ -5313,83 +5313,83 @@
         </is>
       </c>
       <c r="L38" t="n">
-        <v>1.42</v>
+        <v>2.04</v>
       </c>
       <c r="M38" t="n">
-        <v>4.51</v>
+        <v>3.3</v>
       </c>
       <c r="N38" t="n">
-        <v>6.98</v>
+        <v>3.71</v>
       </c>
       <c r="O38" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="P38" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="Q38" t="n">
-        <v>7</v>
+        <v>4.75</v>
       </c>
       <c r="R38" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S38" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="W38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X38" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>['40', '90+1']</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AJ38" t="n">
         <v>2.75</v>
-      </c>
-      <c r="T38" t="n">
-        <v>3</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="X38" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AE38" t="inlineStr">
-        <is>
-          <t>['10', '45+1', '81']</t>
-        </is>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>4</v>
       </c>
       <c r="AK38" s="3" t="n">
         <v>45623.69791666666</v>
@@ -5416,25 +5416,25 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G39" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H39" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" t="n">
         <v>2</v>
       </c>
-      <c r="I39" t="n">
-        <v>0</v>
-      </c>
       <c r="J39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K39" t="inlineStr">
         <is>
@@ -5442,83 +5442,83 @@
         </is>
       </c>
       <c r="L39" t="n">
-        <v>2.04</v>
+        <v>1.42</v>
       </c>
       <c r="M39" t="n">
-        <v>3.3</v>
+        <v>4.51</v>
       </c>
       <c r="N39" t="n">
-        <v>3.71</v>
+        <v>6.98</v>
       </c>
       <c r="O39" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="P39" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>7</v>
+      </c>
+      <c r="R39" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W39" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="X39" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC39" t="n">
         <v>2.1</v>
       </c>
-      <c r="Q39" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="R39" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S39" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T39" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U39" t="n">
+      <c r="AD39" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>['10', '45+1', '81']</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG39" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AI39" t="n">
         <v>1.33</v>
       </c>
-      <c r="V39" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W39" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="X39" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Y39" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Z39" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AA39" t="n">
+      <c r="AJ39" t="n">
         <v>4</v>
-      </c>
-      <c r="AB39" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC39" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD39" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE39" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF39" t="inlineStr">
-        <is>
-          <t>['40', '90+1']</t>
-        </is>
-      </c>
-      <c r="AG39" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH39" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>2.75</v>
       </c>
       <c r="AK39" s="3" t="n">
         <v>45623.69791666666</v>
@@ -5674,25 +5674,25 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>PSV</t>
+          <t>Celtic</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Shakhtar Donetsk</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
       </c>
       <c r="J41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K41" t="inlineStr">
         <is>
@@ -5700,83 +5700,83 @@
         </is>
       </c>
       <c r="L41" t="n">
-        <v>1.36</v>
+        <v>2.09</v>
       </c>
       <c r="M41" t="n">
-        <v>5.06</v>
+        <v>3.54</v>
       </c>
       <c r="N41" t="n">
-        <v>7.38</v>
+        <v>3.32</v>
       </c>
       <c r="O41" t="n">
-        <v>1.91</v>
+        <v>2.6</v>
       </c>
       <c r="P41" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>4</v>
+      </c>
+      <c r="R41" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S41" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T41" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q41" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R41" t="n">
+      <c r="U41" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W41" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="X41" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>['60']</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>['26']</t>
+        </is>
+      </c>
+      <c r="AG41" t="n">
         <v>1.29</v>
       </c>
-      <c r="S41" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T41" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="U41" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W41" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="X41" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z41" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AA41" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AC41" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD41" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE41" t="inlineStr">
-        <is>
-          <t>['87', '90', '90+5']</t>
-        </is>
-      </c>
-      <c r="AF41" t="inlineStr">
-        <is>
-          <t>['8', '37']</t>
-        </is>
-      </c>
-      <c r="AG41" t="n">
-        <v>1.09</v>
-      </c>
       <c r="AH41" t="n">
-        <v>2.99</v>
+        <v>1.87</v>
       </c>
       <c r="AI41" t="n">
-        <v>1.29</v>
+        <v>1.57</v>
       </c>
       <c r="AJ41" t="n">
-        <v>3.6</v>
+        <v>2.4</v>
       </c>
       <c r="AK41" s="3" t="n">
         <v>45623.70833333334</v>
@@ -5803,25 +5803,25 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Bologna</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="G42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
         <v>0</v>
       </c>
       <c r="J42" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K42" t="inlineStr">
         <is>
@@ -5829,83 +5829,83 @@
         </is>
       </c>
       <c r="L42" t="n">
-        <v>2.67</v>
+        <v>2.2</v>
       </c>
       <c r="M42" t="n">
-        <v>3.23</v>
+        <v>3.63</v>
       </c>
       <c r="N42" t="n">
-        <v>2.67</v>
+        <v>3.03</v>
       </c>
       <c r="O42" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
       <c r="P42" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="R42" t="n">
-        <v>1.44</v>
+        <v>1.29</v>
       </c>
       <c r="S42" t="n">
-        <v>2.63</v>
+        <v>3.5</v>
       </c>
       <c r="T42" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="U42" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="V42" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="W42" t="n">
-        <v>1.35</v>
+        <v>1.17</v>
       </c>
       <c r="X42" t="n">
-        <v>3.35</v>
+        <v>5.3</v>
       </c>
       <c r="Y42" t="n">
-        <v>1.95</v>
+        <v>1.53</v>
       </c>
       <c r="Z42" t="n">
-        <v>1.85</v>
+        <v>2.45</v>
       </c>
       <c r="AA42" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
       <c r="AB42" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AC42" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AD42" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="AE42" t="inlineStr">
         <is>
-          <t>['63']</t>
+          <t>['52', '76']</t>
         </is>
       </c>
       <c r="AF42" t="inlineStr">
         <is>
-          <t>['44', '66']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG42" t="n">
-        <v>1.44</v>
+        <v>1.32</v>
       </c>
       <c r="AH42" t="n">
-        <v>1.59</v>
+        <v>1.86</v>
       </c>
       <c r="AI42" t="n">
-        <v>1.8</v>
+        <v>1.57</v>
       </c>
       <c r="AJ42" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AK42" s="3" t="n">
         <v>45623.70833333334</v>
@@ -6061,19 +6061,19 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Dinamo Zagreb</t>
+          <t>Bologna</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I44" t="n">
         <v>0</v>
@@ -6087,83 +6087,83 @@
         </is>
       </c>
       <c r="L44" t="n">
-        <v>4.22</v>
+        <v>2.67</v>
       </c>
       <c r="M44" t="n">
-        <v>4</v>
+        <v>3.23</v>
       </c>
       <c r="N44" t="n">
-        <v>1.73</v>
+        <v>2.67</v>
       </c>
       <c r="O44" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="P44" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.25</v>
+        <v>3.6</v>
       </c>
       <c r="R44" t="n">
-        <v>1.29</v>
+        <v>1.44</v>
       </c>
       <c r="S44" t="n">
-        <v>3.5</v>
+        <v>2.63</v>
       </c>
       <c r="T44" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="U44" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="V44" t="n">
-        <v>1.03</v>
+        <v>1.07</v>
       </c>
       <c r="W44" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="X44" t="n">
-        <v>5</v>
+        <v>3.35</v>
       </c>
       <c r="Y44" t="n">
-        <v>1.57</v>
+        <v>1.95</v>
       </c>
       <c r="Z44" t="n">
-        <v>2.25</v>
+        <v>1.85</v>
       </c>
       <c r="AA44" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>['63']</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>['44', '66']</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AJ44" t="n">
         <v>2.2</v>
-      </c>
-      <c r="AB44" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC44" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD44" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE44" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>['41', '56', '90']</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AH44" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI44" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AJ44" t="n">
-        <v>1.5</v>
       </c>
       <c r="AK44" s="3" t="n">
         <v>45623.70833333334</v>
@@ -6190,25 +6190,25 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Celtic</t>
+          <t>PSV</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Shakhtar Donetsk</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K45" t="inlineStr">
         <is>
@@ -6216,83 +6216,83 @@
         </is>
       </c>
       <c r="L45" t="n">
-        <v>2.09</v>
+        <v>1.36</v>
       </c>
       <c r="M45" t="n">
-        <v>3.54</v>
+        <v>5.06</v>
       </c>
       <c r="N45" t="n">
-        <v>3.32</v>
+        <v>7.38</v>
       </c>
       <c r="O45" t="n">
-        <v>2.6</v>
+        <v>1.91</v>
       </c>
       <c r="P45" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R45" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S45" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V45" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W45" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X45" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z45" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q45" t="n">
-        <v>4</v>
-      </c>
-      <c r="R45" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="S45" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T45" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U45" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V45" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W45" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="X45" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="Z45" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AA45" t="n">
-        <v>2.8</v>
+        <v>2.59</v>
       </c>
       <c r="AB45" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AC45" t="n">
-        <v>1.57</v>
+        <v>1.8</v>
       </c>
       <c r="AD45" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AE45" t="inlineStr">
         <is>
-          <t>['60']</t>
+          <t>['87', '90', '90+5']</t>
         </is>
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>['26']</t>
+          <t>['8', '37']</t>
         </is>
       </c>
       <c r="AG45" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AI45" t="n">
         <v>1.29</v>
       </c>
-      <c r="AH45" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AI45" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AJ45" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
       <c r="AK45" s="3" t="n">
         <v>45623.70833333334</v>
@@ -6319,25 +6319,25 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Dinamo Zagreb</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K46" t="inlineStr">
         <is>
@@ -6345,22 +6345,22 @@
         </is>
       </c>
       <c r="L46" t="n">
-        <v>2.2</v>
+        <v>4.22</v>
       </c>
       <c r="M46" t="n">
-        <v>3.63</v>
+        <v>4</v>
       </c>
       <c r="N46" t="n">
-        <v>3.03</v>
+        <v>1.73</v>
       </c>
       <c r="O46" t="n">
-        <v>2.5</v>
+        <v>4.5</v>
       </c>
       <c r="P46" t="n">
         <v>2.4</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.75</v>
+        <v>2.25</v>
       </c>
       <c r="R46" t="n">
         <v>1.29</v>
@@ -6369,59 +6369,59 @@
         <v>3.5</v>
       </c>
       <c r="T46" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="V46" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W46" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="X46" t="n">
+        <v>5</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z46" t="n">
         <v>2.25</v>
       </c>
-      <c r="U46" t="n">
+      <c r="AA46" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC46" t="n">
         <v>1.57</v>
       </c>
-      <c r="V46" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W46" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="X46" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z46" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA46" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AC46" t="n">
+      <c r="AD46" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE46" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF46" t="inlineStr">
+        <is>
+          <t>['41', '56', '90']</t>
+        </is>
+      </c>
+      <c r="AG46" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AH46" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI46" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AJ46" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AD46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AE46" t="inlineStr">
-        <is>
-          <t>['52', '76']</t>
-        </is>
-      </c>
-      <c r="AF46" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG46" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AH46" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AI46" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AJ46" t="n">
-        <v>2.3</v>
       </c>
       <c r="AK46" s="3" t="n">
         <v>45623.70833333334</v>
